--- a/Tiempos Rendimiento.xlsx
+++ b/Tiempos Rendimiento.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/branthonycc/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celes\Desktop\IterativoVsRecursivo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73E8DBB2-0652-E543-BEAE-10379D709781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A624E3A8-AA17-48F4-8D66-C331DAE2A9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12509" yWindow="75" windowWidth="11533" windowHeight="12722" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guia de Uso" sheetId="1" r:id="rId1"/>
@@ -567,46 +567,6 @@
   </cellStyleXfs>
   <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -697,6 +657,46 @@
     <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -785,7 +785,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -938,22 +938,22 @@
                 <c:formatCode>#,##0.000000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>2.6200000000000003E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>2.1400000000000004E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3.6400000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>4.4800000000000005E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>5.04E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.19064</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1075,22 +1075,22 @@
                 <c:formatCode>#,##0.000000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>2.4399999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>2.6600000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>2.9199999999999994E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>3.3799999999999998E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>3.4600000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>3.1099999999999995E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1340,7 +1340,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -1493,22 +1493,22 @@
                 <c:formatCode>#,##0.000000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>2.8799999999999995E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>5.62E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>5.6519999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>4.7800000000000002E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.3100000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1.16E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1630,22 +1630,22 @@
                 <c:formatCode>#,##0.000000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>2.0800000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>5.2599999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>5.7959999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>5.5909999999999994E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.42469999999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>4.9792620000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1895,7 +1895,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -2045,19 +2045,19 @@
                 <c:formatCode>#,##0.000000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>2.4200000000000003E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>2.72E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>2.9599999999999993E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>2.8399999999999996E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>7.2399999999999993E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2176,19 +2176,19 @@
                 <c:formatCode>#,##0.000000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>6.2399999999999988E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>3.0800000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>5.0600000000000005E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>3.9199999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>9.1E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2438,7 +2438,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -2588,19 +2588,19 @@
                 <c:formatCode>#,##0.000000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>2.5739999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1.542E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1.4859999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1.7139999999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.14933399999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2719,19 +2719,19 @@
                 <c:formatCode>#,##0.000000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.5E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>2.408E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>4.5500000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>2.1099999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.6280000000000003E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3322,7 +3322,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -3330,114 +3330,125 @@
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="14" t="s">
+    <row r="1" spans="2:4" ht="5.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-    </row>
-    <row r="3" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="13" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+    </row>
+    <row r="3" spans="2:4" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-    </row>
-    <row r="4" spans="2:4" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="12" t="s">
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+    </row>
+    <row r="4" spans="2:4" ht="9.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:4" ht="27.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="11"/>
-    </row>
-    <row r="6" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="12"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-    </row>
-    <row r="7" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="12" t="s">
+      <c r="D5" s="35"/>
+    </row>
+    <row r="6" spans="2:4" ht="59.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="31"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+    </row>
+    <row r="7" spans="2:4" ht="5.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="2:4" ht="27.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="2:4" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="12"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-    </row>
-    <row r="10" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="12" t="s">
+      <c r="D8" s="32"/>
+    </row>
+    <row r="9" spans="2:4" ht="117.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="31"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+    </row>
+    <row r="10" spans="2:4" ht="5.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="2:4" ht="27.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" spans="2:4" ht="81.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="12"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-    </row>
-    <row r="13" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="12" t="s">
+      <c r="D11" s="32"/>
+    </row>
+    <row r="12" spans="2:4" ht="81.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="31"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+    </row>
+    <row r="13" spans="2:4" ht="5.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="2:4" ht="27.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" spans="2:4" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="12"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-    </row>
-    <row r="16" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="12" t="s">
+      <c r="D14" s="34"/>
+    </row>
+    <row r="15" spans="2:4" ht="99.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="31"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+    </row>
+    <row r="16" spans="2:4" ht="5.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="2:4" ht="27.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="11"/>
-    </row>
-    <row r="18" spans="2:4" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="12"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-    </row>
-    <row r="19" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="12" t="s">
+      <c r="D17" s="35"/>
+    </row>
+    <row r="18" spans="2:4" ht="99.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="31"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+    </row>
+    <row r="19" spans="2:4" ht="5.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="2:4" ht="27.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="9"/>
-    </row>
-    <row r="21" spans="2:4" ht="81.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="12"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-    </row>
-    <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="D20" s="32"/>
+    </row>
+    <row r="21" spans="2:4" ht="81.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="31"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+    </row>
+    <row r="22" spans="2:4" ht="5.95" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C21:D21"/>
@@ -3447,17 +3458,6 @@
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3466,10 +3466,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:J52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="1" max="1" width="12" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="9" width="12" customWidth="1"/>
@@ -3477,1379 +3477,1379 @@
     <col min="11" max="11" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="7" t="s">
+    <row r="1" spans="2:10" ht="33.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-    </row>
-    <row r="2" spans="2:10" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="15" t="s">
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+    </row>
+    <row r="2" spans="2:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="17" t="s">
+    <row r="3" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="5">
         <v>5</v>
       </c>
-      <c r="E3" s="20">
-        <v>0</v>
-      </c>
-      <c r="F3" s="20">
-        <v>0</v>
-      </c>
-      <c r="G3" s="20">
-        <v>0</v>
-      </c>
-      <c r="H3" s="20">
-        <v>0</v>
-      </c>
-      <c r="I3" s="20">
-        <v>0</v>
-      </c>
-      <c r="J3" s="21">
+      <c r="E3" s="6">
+        <v>2.7E-4</v>
+      </c>
+      <c r="F3" s="6">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1.9000000000000001E-4</v>
+      </c>
+      <c r="H3" s="6">
+        <v>3.6000000000000002E-4</v>
+      </c>
+      <c r="I3" s="6">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="J3" s="7">
         <f t="shared" ref="J3:J14" si="0">AVERAGE(E3:I3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="17" t="s">
+        <v>2.6200000000000003E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="5">
         <v>10</v>
       </c>
-      <c r="E4" s="20">
-        <v>0</v>
-      </c>
-      <c r="F4" s="20">
-        <v>0</v>
-      </c>
-      <c r="G4" s="20">
-        <v>0</v>
-      </c>
-      <c r="H4" s="20">
-        <v>0</v>
-      </c>
-      <c r="I4" s="20">
-        <v>0</v>
-      </c>
-      <c r="J4" s="21">
+      <c r="E4" s="6">
+        <v>5.5000000000000003E-4</v>
+      </c>
+      <c r="F4" s="6">
+        <v>7.2000000000000005E-4</v>
+      </c>
+      <c r="G4" s="6">
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="H4" s="6">
+        <v>8.1799999999999998E-3</v>
+      </c>
+      <c r="I4" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J4" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="17" t="s">
+        <v>2.1400000000000004E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="5">
         <v>15</v>
       </c>
-      <c r="E5" s="20">
-        <v>0</v>
-      </c>
-      <c r="F5" s="20">
-        <v>0</v>
-      </c>
-      <c r="G5" s="20">
-        <v>0</v>
-      </c>
-      <c r="H5" s="20">
-        <v>0</v>
-      </c>
-      <c r="I5" s="20">
-        <v>0</v>
-      </c>
-      <c r="J5" s="21">
+      <c r="E5" s="6">
+        <v>4.2999999999999999E-4</v>
+      </c>
+      <c r="F5" s="6">
+        <v>3.3E-4</v>
+      </c>
+      <c r="G5" s="6">
+        <v>3.5E-4</v>
+      </c>
+      <c r="H5" s="6">
+        <v>3.6999999999999999E-4</v>
+      </c>
+      <c r="I5" s="6">
+        <v>3.4000000000000002E-4</v>
+      </c>
+      <c r="J5" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="17" t="s">
+        <v>3.6400000000000001E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="5">
         <v>20</v>
       </c>
-      <c r="E6" s="20">
-        <v>0</v>
-      </c>
-      <c r="F6" s="20">
-        <v>0</v>
-      </c>
-      <c r="G6" s="20">
-        <v>0</v>
-      </c>
-      <c r="H6" s="20">
-        <v>0</v>
-      </c>
-      <c r="I6" s="20">
-        <v>0</v>
-      </c>
-      <c r="J6" s="21">
+      <c r="E6" s="6">
+        <v>4.4999999999999999E-4</v>
+      </c>
+      <c r="F6" s="6">
+        <v>4.0999999999999999E-4</v>
+      </c>
+      <c r="G6" s="6">
+        <v>4.8000000000000001E-4</v>
+      </c>
+      <c r="H6" s="6">
+        <v>4.4000000000000002E-4</v>
+      </c>
+      <c r="I6" s="6">
+        <v>4.6000000000000001E-4</v>
+      </c>
+      <c r="J6" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="17" t="s">
+        <v>4.4800000000000005E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="5">
         <v>25</v>
       </c>
-      <c r="E7" s="20">
-        <v>0</v>
-      </c>
-      <c r="F7" s="20">
-        <v>0</v>
-      </c>
-      <c r="G7" s="20">
-        <v>0</v>
-      </c>
-      <c r="H7" s="20">
-        <v>0</v>
-      </c>
-      <c r="I7" s="20">
-        <v>0</v>
-      </c>
-      <c r="J7" s="21">
+      <c r="E7" s="6">
+        <v>5.5000000000000003E-4</v>
+      </c>
+      <c r="F7" s="6">
+        <v>4.6000000000000001E-4</v>
+      </c>
+      <c r="G7" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="H7" s="6">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="I7" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J7" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="17" t="s">
+        <v>5.04E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="5">
         <v>30</v>
       </c>
-      <c r="E8" s="20">
-        <v>0</v>
-      </c>
-      <c r="F8" s="20">
-        <v>0</v>
-      </c>
-      <c r="G8" s="20">
-        <v>0</v>
-      </c>
-      <c r="H8" s="20">
-        <v>0</v>
-      </c>
-      <c r="I8" s="20">
-        <v>0</v>
-      </c>
-      <c r="J8" s="21">
+      <c r="E8" s="6">
+        <v>0.15762000000000001</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.24751000000000001</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.17279</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.24565000000000001</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.12963</v>
+      </c>
+      <c r="J8" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="22" t="s">
+        <v>0.19064</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="10">
         <v>5</v>
       </c>
-      <c r="E9" s="20">
-        <v>0</v>
-      </c>
-      <c r="F9" s="20">
-        <v>0</v>
-      </c>
-      <c r="G9" s="20">
-        <v>0</v>
-      </c>
-      <c r="H9" s="20">
-        <v>0</v>
-      </c>
-      <c r="I9" s="20">
-        <v>0</v>
-      </c>
-      <c r="J9" s="21">
+      <c r="E9" s="6">
+        <v>2.9E-4</v>
+      </c>
+      <c r="F9" s="6">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="G9" s="6">
+        <v>2.1000000000000001E-4</v>
+      </c>
+      <c r="H9" s="6">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="I9" s="6">
+        <v>2.7E-4</v>
+      </c>
+      <c r="J9" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="22" t="s">
+        <v>2.4399999999999999E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="10">
         <v>10</v>
       </c>
-      <c r="E10" s="20">
-        <v>0</v>
-      </c>
-      <c r="F10" s="20">
-        <v>0</v>
-      </c>
-      <c r="G10" s="20">
-        <v>0</v>
-      </c>
-      <c r="H10" s="20">
-        <v>0</v>
-      </c>
-      <c r="I10" s="20">
-        <v>0</v>
-      </c>
-      <c r="J10" s="21">
+      <c r="E10" s="6">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F10" s="6">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="G10" s="6">
+        <v>2.5999999999999998E-4</v>
+      </c>
+      <c r="H10" s="6">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="I10" s="6">
+        <v>2.7E-4</v>
+      </c>
+      <c r="J10" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="22" t="s">
+        <v>2.6600000000000001E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="10">
         <v>15</v>
       </c>
-      <c r="E11" s="20">
-        <v>0</v>
-      </c>
-      <c r="F11" s="20">
-        <v>0</v>
-      </c>
-      <c r="G11" s="20">
-        <v>0</v>
-      </c>
-      <c r="H11" s="20">
-        <v>0</v>
-      </c>
-      <c r="I11" s="20">
-        <v>0</v>
-      </c>
-      <c r="J11" s="21">
+      <c r="E11" s="6">
+        <v>2.7999999999999998E-4</v>
+      </c>
+      <c r="F11" s="6">
+        <v>2.5999999999999998E-4</v>
+      </c>
+      <c r="G11" s="6">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="H11" s="6">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="I11" s="6">
+        <v>3.2000000000000003E-4</v>
+      </c>
+      <c r="J11" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="22" t="s">
+        <v>2.9199999999999994E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="10">
         <v>20</v>
       </c>
-      <c r="E12" s="20">
-        <v>0</v>
-      </c>
-      <c r="F12" s="20">
-        <v>0</v>
-      </c>
-      <c r="G12" s="20">
-        <v>0</v>
-      </c>
-      <c r="H12" s="20">
-        <v>0</v>
-      </c>
-      <c r="I12" s="20">
-        <v>0</v>
-      </c>
-      <c r="J12" s="21">
+      <c r="E12" s="6">
+        <v>3.3E-4</v>
+      </c>
+      <c r="F12" s="6">
+        <v>3.8999999999999999E-4</v>
+      </c>
+      <c r="G12" s="6">
+        <v>3.3E-4</v>
+      </c>
+      <c r="H12" s="6">
+        <v>3.1E-4</v>
+      </c>
+      <c r="I12" s="6">
+        <v>3.3E-4</v>
+      </c>
+      <c r="J12" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="22" t="s">
+        <v>3.3799999999999998E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="10">
         <v>25</v>
       </c>
-      <c r="E13" s="20">
-        <v>0</v>
-      </c>
-      <c r="F13" s="20">
-        <v>0</v>
-      </c>
-      <c r="G13" s="20">
-        <v>0</v>
-      </c>
-      <c r="H13" s="20">
-        <v>0</v>
-      </c>
-      <c r="I13" s="20">
-        <v>0</v>
-      </c>
-      <c r="J13" s="21">
+      <c r="E13" s="6">
+        <v>3.3E-4</v>
+      </c>
+      <c r="F13" s="6">
+        <v>3.2000000000000003E-4</v>
+      </c>
+      <c r="G13" s="6">
+        <v>2.9E-4</v>
+      </c>
+      <c r="H13" s="6">
+        <v>2.9E-4</v>
+      </c>
+      <c r="I13" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J13" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="22" t="s">
+        <v>3.4600000000000001E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="10">
         <v>30</v>
       </c>
-      <c r="E14" s="20">
-        <v>0</v>
-      </c>
-      <c r="F14" s="20">
-        <v>0</v>
-      </c>
-      <c r="G14" s="20">
-        <v>0</v>
-      </c>
-      <c r="H14" s="20">
-        <v>0</v>
-      </c>
-      <c r="I14" s="20">
-        <v>0</v>
-      </c>
-      <c r="J14" s="21">
+      <c r="E14" s="6">
+        <v>2.8400000000000001E-3</v>
+      </c>
+      <c r="F14" s="6">
+        <v>2.82E-3</v>
+      </c>
+      <c r="G14" s="6">
+        <v>3.4199999999999999E-3</v>
+      </c>
+      <c r="H14" s="6">
+        <v>3.3899999999999998E-3</v>
+      </c>
+      <c r="I14" s="6">
+        <v>3.0799999999999998E-3</v>
+      </c>
+      <c r="J14" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="17" t="s">
+        <v>3.1099999999999995E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="5">
         <v>5</v>
       </c>
-      <c r="E16" s="20">
-        <v>0</v>
-      </c>
-      <c r="F16" s="20">
-        <v>0</v>
-      </c>
-      <c r="G16" s="20">
-        <v>0</v>
-      </c>
-      <c r="H16" s="20">
-        <v>0</v>
-      </c>
-      <c r="I16" s="20">
-        <v>0</v>
-      </c>
-      <c r="J16" s="21">
+      <c r="E16" s="6">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F16" s="6">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="G16" s="6">
+        <v>2.7999999999999998E-4</v>
+      </c>
+      <c r="H16" s="6">
+        <v>2.2000000000000001E-4</v>
+      </c>
+      <c r="I16" s="6">
+        <v>3.4000000000000002E-4</v>
+      </c>
+      <c r="J16" s="7">
         <f t="shared" ref="J16:J27" si="1">AVERAGE(E16:I16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="17" t="s">
+        <v>2.8799999999999995E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="5">
         <v>10</v>
       </c>
-      <c r="E17" s="20">
-        <v>0</v>
-      </c>
-      <c r="F17" s="20">
-        <v>0</v>
-      </c>
-      <c r="G17" s="20">
-        <v>0</v>
-      </c>
-      <c r="H17" s="20">
-        <v>0</v>
-      </c>
-      <c r="I17" s="20">
-        <v>0</v>
-      </c>
-      <c r="J17" s="21">
+      <c r="E17" s="6">
+        <v>4.6000000000000001E-4</v>
+      </c>
+      <c r="F17" s="6">
+        <v>4.0999999999999999E-4</v>
+      </c>
+      <c r="G17" s="6">
+        <v>6.2E-4</v>
+      </c>
+      <c r="H17" s="6">
+        <v>5.9000000000000003E-4</v>
+      </c>
+      <c r="I17" s="6">
+        <v>7.2999999999999996E-4</v>
+      </c>
+      <c r="J17" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="17" t="s">
+        <v>5.62E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="5">
         <v>15</v>
       </c>
-      <c r="E18" s="20">
-        <v>0</v>
-      </c>
-      <c r="F18" s="20">
-        <v>0</v>
-      </c>
-      <c r="G18" s="20">
-        <v>0</v>
-      </c>
-      <c r="H18" s="20">
-        <v>0</v>
-      </c>
-      <c r="I18" s="20">
-        <v>0</v>
-      </c>
-      <c r="J18" s="21">
+      <c r="E18" s="6">
+        <v>3.2000000000000003E-4</v>
+      </c>
+      <c r="F18" s="6">
+        <v>4.4999999999999999E-4</v>
+      </c>
+      <c r="G18" s="6">
+        <v>4.6999999999999999E-4</v>
+      </c>
+      <c r="H18" s="6">
+        <v>2.6519999999999998E-2</v>
+      </c>
+      <c r="I18" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J18" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="17" t="s">
+        <v>5.6519999999999999E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="5">
         <v>20</v>
       </c>
-      <c r="E19" s="20">
-        <v>0</v>
-      </c>
-      <c r="F19" s="20">
-        <v>0</v>
-      </c>
-      <c r="G19" s="20">
-        <v>0</v>
-      </c>
-      <c r="H19" s="20">
-        <v>0</v>
-      </c>
-      <c r="I19" s="20">
-        <v>0</v>
-      </c>
-      <c r="J19" s="21">
+      <c r="E19" s="6">
+        <v>5.5999999999999995E-4</v>
+      </c>
+      <c r="F19" s="6">
+        <v>4.8999999999999998E-4</v>
+      </c>
+      <c r="G19" s="6">
+        <v>4.4999999999999999E-4</v>
+      </c>
+      <c r="H19" s="6">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="I19" s="6">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="J19" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="17" t="s">
+        <v>4.7800000000000002E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="5">
         <v>25</v>
       </c>
-      <c r="E20" s="20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="20">
-        <v>0</v>
-      </c>
-      <c r="G20" s="20">
-        <v>0</v>
-      </c>
-      <c r="H20" s="20">
-        <v>0</v>
-      </c>
-      <c r="I20" s="20">
-        <v>0</v>
-      </c>
-      <c r="J20" s="21">
+      <c r="E20" s="6">
+        <v>4.4400000000000004E-3</v>
+      </c>
+      <c r="F20" s="6">
+        <v>5.6999999999999998E-4</v>
+      </c>
+      <c r="G20" s="6">
+        <v>4.6999999999999999E-4</v>
+      </c>
+      <c r="H20" s="6">
+        <v>6.3000000000000003E-4</v>
+      </c>
+      <c r="I20" s="6">
+        <v>4.4000000000000002E-4</v>
+      </c>
+      <c r="J20" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="17" t="s">
+        <v>1.3100000000000002E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="5">
         <v>30</v>
       </c>
-      <c r="E21" s="20">
-        <v>0</v>
-      </c>
-      <c r="F21" s="20">
-        <v>0</v>
-      </c>
-      <c r="G21" s="20">
-        <v>0</v>
-      </c>
-      <c r="H21" s="20">
-        <v>0</v>
-      </c>
-      <c r="I21" s="20">
-        <v>0</v>
-      </c>
-      <c r="J21" s="21">
+      <c r="E21" s="6">
+        <v>1.2600000000000001E-3</v>
+      </c>
+      <c r="F21" s="6">
+        <v>9.2000000000000003E-4</v>
+      </c>
+      <c r="G21" s="6">
+        <v>1.2099999999999999E-3</v>
+      </c>
+      <c r="H21" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="I21" s="6">
+        <v>1.41E-3</v>
+      </c>
+      <c r="J21" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="22" t="s">
+        <v>1.16E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="10">
         <v>5</v>
       </c>
-      <c r="E22" s="20">
-        <v>0</v>
-      </c>
-      <c r="F22" s="20">
-        <v>0</v>
-      </c>
-      <c r="G22" s="20">
-        <v>0</v>
-      </c>
-      <c r="H22" s="20">
-        <v>0</v>
-      </c>
-      <c r="I22" s="20">
-        <v>0</v>
-      </c>
-      <c r="J22" s="21">
+      <c r="E22" s="6">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="F22" s="6">
+        <v>2.3000000000000001E-4</v>
+      </c>
+      <c r="G22" s="6">
+        <v>2.1000000000000001E-4</v>
+      </c>
+      <c r="H22" s="6">
+        <v>2.2000000000000001E-4</v>
+      </c>
+      <c r="I22" s="6">
+        <v>2.3000000000000001E-4</v>
+      </c>
+      <c r="J22" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="22" t="s">
+        <v>2.0800000000000001E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="10">
         <v>10</v>
       </c>
-      <c r="E23" s="20">
-        <v>0</v>
-      </c>
-      <c r="F23" s="20">
-        <v>0</v>
-      </c>
-      <c r="G23" s="20">
-        <v>0</v>
-      </c>
-      <c r="H23" s="20">
-        <v>0</v>
-      </c>
-      <c r="I23" s="20">
-        <v>0</v>
-      </c>
-      <c r="J23" s="21">
+      <c r="E23" s="6">
+        <v>5.1999999999999995E-4</v>
+      </c>
+      <c r="F23" s="6">
+        <v>3.6999999999999999E-4</v>
+      </c>
+      <c r="G23" s="6">
+        <v>7.2000000000000005E-4</v>
+      </c>
+      <c r="H23" s="6">
+        <v>5.1999999999999995E-4</v>
+      </c>
+      <c r="I23" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J23" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="22" t="s">
+        <v>5.2599999999999999E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="10">
         <v>15</v>
       </c>
-      <c r="E24" s="20">
-        <v>0</v>
-      </c>
-      <c r="F24" s="20">
-        <v>0</v>
-      </c>
-      <c r="G24" s="20">
-        <v>0</v>
-      </c>
-      <c r="H24" s="20">
-        <v>0</v>
-      </c>
-      <c r="I24" s="20">
-        <v>0</v>
-      </c>
-      <c r="J24" s="21">
+      <c r="E24" s="6">
+        <v>7.8799999999999999E-3</v>
+      </c>
+      <c r="F24" s="6">
+        <v>3.8800000000000002E-3</v>
+      </c>
+      <c r="G24" s="6">
+        <v>3.5699999999999998E-3</v>
+      </c>
+      <c r="H24" s="6">
+        <v>3.6600000000000001E-3</v>
+      </c>
+      <c r="I24" s="6">
+        <v>9.9900000000000006E-3</v>
+      </c>
+      <c r="J24" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="22" t="s">
+        <v>5.7959999999999999E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="10">
         <v>20</v>
       </c>
-      <c r="E25" s="20">
-        <v>0</v>
-      </c>
-      <c r="F25" s="20">
-        <v>0</v>
-      </c>
-      <c r="G25" s="20">
-        <v>0</v>
-      </c>
-      <c r="H25" s="20">
-        <v>0</v>
-      </c>
-      <c r="I25" s="20">
-        <v>0</v>
-      </c>
-      <c r="J25" s="21">
+      <c r="E25" s="6">
+        <v>6.08E-2</v>
+      </c>
+      <c r="F25" s="6">
+        <v>3.0849999999999999E-2</v>
+      </c>
+      <c r="G25" s="6">
+        <v>8.9120000000000005E-2</v>
+      </c>
+      <c r="H25" s="6">
+        <v>4.385E-2</v>
+      </c>
+      <c r="I25" s="6">
+        <v>5.493E-2</v>
+      </c>
+      <c r="J25" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="22" t="s">
+        <v>5.5909999999999994E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="10">
         <v>25</v>
       </c>
-      <c r="E26" s="20">
-        <v>0</v>
-      </c>
-      <c r="F26" s="20">
-        <v>0</v>
-      </c>
-      <c r="G26" s="20">
-        <v>0</v>
-      </c>
-      <c r="H26" s="20">
-        <v>0</v>
-      </c>
-      <c r="I26" s="20">
-        <v>0</v>
-      </c>
-      <c r="J26" s="21">
+      <c r="E26" s="6">
+        <v>0.36403000000000002</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0.78134000000000003</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0.31603999999999999</v>
+      </c>
+      <c r="H26" s="6">
+        <v>0.32797999999999999</v>
+      </c>
+      <c r="I26" s="6">
+        <v>0.33411000000000002</v>
+      </c>
+      <c r="J26" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="22" t="s">
+        <v>0.42469999999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="10">
         <v>30</v>
       </c>
-      <c r="E27" s="20">
-        <v>0</v>
-      </c>
-      <c r="F27" s="20">
-        <v>0</v>
-      </c>
-      <c r="G27" s="20">
-        <v>0</v>
-      </c>
-      <c r="H27" s="20">
-        <v>0</v>
-      </c>
-      <c r="I27" s="20">
-        <v>0</v>
-      </c>
-      <c r="J27" s="21">
+      <c r="E27" s="6">
+        <v>5.0592699999999997</v>
+      </c>
+      <c r="F27" s="6">
+        <v>5.3677200000000003</v>
+      </c>
+      <c r="G27" s="6">
+        <v>4.9855799999999997</v>
+      </c>
+      <c r="H27" s="6">
+        <v>5.0426799999999998</v>
+      </c>
+      <c r="I27" s="6">
+        <v>4.4410600000000002</v>
+      </c>
+      <c r="J27" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="17" t="s">
+        <v>4.9792620000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="5">
         <v>100</v>
       </c>
-      <c r="E29" s="20">
-        <v>0</v>
-      </c>
-      <c r="F29" s="20">
-        <v>0</v>
-      </c>
-      <c r="G29" s="20">
-        <v>0</v>
-      </c>
-      <c r="H29" s="20">
-        <v>0</v>
-      </c>
-      <c r="I29" s="20">
-        <v>0</v>
-      </c>
-      <c r="J29" s="21">
+      <c r="E29" s="6">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="F29" s="6">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="G29" s="6">
+        <v>2.7999999999999998E-4</v>
+      </c>
+      <c r="H29" s="6">
+        <v>2.3000000000000001E-4</v>
+      </c>
+      <c r="I29" s="6">
+        <v>2.1000000000000001E-4</v>
+      </c>
+      <c r="J29" s="7">
         <f t="shared" ref="J29:J38" si="2">AVERAGE(E29:I29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="17" t="s">
+        <v>2.4200000000000003E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="5">
         <v>500</v>
       </c>
-      <c r="E30" s="20">
-        <v>0</v>
-      </c>
-      <c r="F30" s="20">
-        <v>0</v>
-      </c>
-      <c r="G30" s="20">
-        <v>0</v>
-      </c>
-      <c r="H30" s="20">
-        <v>0</v>
-      </c>
-      <c r="I30" s="20">
-        <v>0</v>
-      </c>
-      <c r="J30" s="21">
+      <c r="E30" s="6">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="F30" s="6">
+        <v>2.2000000000000001E-4</v>
+      </c>
+      <c r="G30" s="6">
+        <v>2.9E-4</v>
+      </c>
+      <c r="H30" s="6">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="I30" s="6">
+        <v>3.5E-4</v>
+      </c>
+      <c r="J30" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="17" t="s">
+        <v>2.72E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="5">
         <v>1000</v>
       </c>
-      <c r="E31" s="20">
-        <v>0</v>
-      </c>
-      <c r="F31" s="20">
-        <v>0</v>
-      </c>
-      <c r="G31" s="20">
-        <v>0</v>
-      </c>
-      <c r="H31" s="20">
-        <v>0</v>
-      </c>
-      <c r="I31" s="20">
-        <v>0</v>
-      </c>
-      <c r="J31" s="21">
+      <c r="E31" s="6">
+        <v>3.3E-4</v>
+      </c>
+      <c r="F31" s="6">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="G31" s="6">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="H31" s="6">
+        <v>2.7999999999999998E-4</v>
+      </c>
+      <c r="I31" s="6">
+        <v>2.7E-4</v>
+      </c>
+      <c r="J31" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="17" t="s">
+        <v>2.9599999999999993E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="5">
         <v>5000</v>
       </c>
-      <c r="E32" s="20">
-        <v>0</v>
-      </c>
-      <c r="F32" s="20">
-        <v>0</v>
-      </c>
-      <c r="G32" s="20">
-        <v>0</v>
-      </c>
-      <c r="H32" s="20">
-        <v>0</v>
-      </c>
-      <c r="I32" s="20">
-        <v>0</v>
-      </c>
-      <c r="J32" s="21">
+      <c r="E32" s="6">
+        <v>2.7999999999999998E-4</v>
+      </c>
+      <c r="F32" s="6">
+        <v>2.7E-4</v>
+      </c>
+      <c r="G32" s="6">
+        <v>3.1E-4</v>
+      </c>
+      <c r="H32" s="6">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="I32" s="6">
+        <v>2.5999999999999998E-4</v>
+      </c>
+      <c r="J32" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="17" t="s">
+        <v>2.8399999999999996E-4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="5">
         <v>10000</v>
       </c>
-      <c r="E33" s="20">
-        <v>0</v>
-      </c>
-      <c r="F33" s="20">
-        <v>0</v>
-      </c>
-      <c r="G33" s="20">
-        <v>0</v>
-      </c>
-      <c r="H33" s="20">
-        <v>0</v>
-      </c>
-      <c r="I33" s="20">
-        <v>0</v>
-      </c>
-      <c r="J33" s="21">
+      <c r="E33" s="6">
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="F33" s="6">
+        <v>8.5999999999999998E-4</v>
+      </c>
+      <c r="G33" s="6">
+        <v>7.3999999999999999E-4</v>
+      </c>
+      <c r="H33" s="6">
+        <v>4.8000000000000001E-4</v>
+      </c>
+      <c r="I33" s="6">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="J33" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="22" t="s">
+        <v>7.2399999999999993E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="10">
         <v>100</v>
       </c>
-      <c r="E34" s="20">
-        <v>0</v>
-      </c>
-      <c r="F34" s="20">
-        <v>0</v>
-      </c>
-      <c r="G34" s="20">
-        <v>0</v>
-      </c>
-      <c r="H34" s="20">
-        <v>0</v>
-      </c>
-      <c r="I34" s="20">
-        <v>0</v>
-      </c>
-      <c r="J34" s="21">
+      <c r="E34" s="6">
+        <v>2.7E-4</v>
+      </c>
+      <c r="F34" s="6">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="G34" s="6">
+        <v>1.99E-3</v>
+      </c>
+      <c r="H34" s="6">
+        <v>2.5999999999999998E-4</v>
+      </c>
+      <c r="I34" s="6">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="J34" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="22" t="s">
+        <v>6.2399999999999988E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C35" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D35" s="10">
         <v>500</v>
       </c>
-      <c r="E35" s="20">
-        <v>0</v>
-      </c>
-      <c r="F35" s="20">
-        <v>0</v>
-      </c>
-      <c r="G35" s="20">
-        <v>0</v>
-      </c>
-      <c r="H35" s="20">
-        <v>0</v>
-      </c>
-      <c r="I35" s="20">
-        <v>0</v>
-      </c>
-      <c r="J35" s="21">
+      <c r="E35" s="6">
+        <v>2.9E-4</v>
+      </c>
+      <c r="F35" s="6">
+        <v>2.9E-4</v>
+      </c>
+      <c r="G35" s="6">
+        <v>3.6999999999999999E-4</v>
+      </c>
+      <c r="H35" s="6">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="I35" s="6">
+        <v>2.9E-4</v>
+      </c>
+      <c r="J35" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="22" t="s">
+        <v>3.0800000000000001E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="10">
         <v>1000</v>
       </c>
-      <c r="E36" s="20">
-        <v>0</v>
-      </c>
-      <c r="F36" s="20">
-        <v>0</v>
-      </c>
-      <c r="G36" s="20">
-        <v>0</v>
-      </c>
-      <c r="H36" s="20">
-        <v>0</v>
-      </c>
-      <c r="I36" s="20">
-        <v>0</v>
-      </c>
-      <c r="J36" s="21">
+      <c r="E36" s="6">
+        <v>5.4000000000000001E-4</v>
+      </c>
+      <c r="F36" s="6">
+        <v>5.6999999999999998E-4</v>
+      </c>
+      <c r="G36" s="6">
+        <v>5.5000000000000003E-4</v>
+      </c>
+      <c r="H36" s="6">
+        <v>4.8000000000000001E-4</v>
+      </c>
+      <c r="I36" s="6">
+        <v>3.8999999999999999E-4</v>
+      </c>
+      <c r="J36" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="22" t="s">
+        <v>5.0600000000000005E-4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C37" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="10">
         <v>5000</v>
       </c>
-      <c r="E37" s="20">
-        <v>0</v>
-      </c>
-      <c r="F37" s="20">
-        <v>0</v>
-      </c>
-      <c r="G37" s="20">
-        <v>0</v>
-      </c>
-      <c r="H37" s="20">
-        <v>0</v>
-      </c>
-      <c r="I37" s="20">
-        <v>0</v>
-      </c>
-      <c r="J37" s="21">
+      <c r="E37" s="6">
+        <v>4.4999999999999999E-4</v>
+      </c>
+      <c r="F37" s="6">
+        <v>4.4000000000000002E-4</v>
+      </c>
+      <c r="G37" s="6">
+        <v>3.8999999999999999E-4</v>
+      </c>
+      <c r="H37" s="6">
+        <v>3.6000000000000002E-4</v>
+      </c>
+      <c r="I37" s="6">
+        <v>3.2000000000000003E-4</v>
+      </c>
+      <c r="J37" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="22" t="s">
+        <v>3.9199999999999999E-4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="24">
+      <c r="D38" s="10">
         <v>10000</v>
       </c>
-      <c r="E38" s="20">
-        <v>0</v>
-      </c>
-      <c r="F38" s="20">
-        <v>0</v>
-      </c>
-      <c r="G38" s="20">
-        <v>0</v>
-      </c>
-      <c r="H38" s="20">
-        <v>0</v>
-      </c>
-      <c r="I38" s="20">
-        <v>0</v>
-      </c>
-      <c r="J38" s="21">
+      <c r="E38" s="6">
+        <v>1.2700000000000001E-3</v>
+      </c>
+      <c r="F38" s="6">
+        <v>4.0999999999999999E-4</v>
+      </c>
+      <c r="G38" s="6">
+        <v>7.2000000000000005E-4</v>
+      </c>
+      <c r="H38" s="6">
+        <v>9.2000000000000003E-4</v>
+      </c>
+      <c r="I38" s="6">
+        <v>1.23E-3</v>
+      </c>
+      <c r="J38" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="17" t="s">
+        <v>9.1E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="5">
         <v>100</v>
       </c>
-      <c r="E40" s="20">
-        <v>0</v>
-      </c>
-      <c r="F40" s="20">
-        <v>0</v>
-      </c>
-      <c r="G40" s="20">
-        <v>0</v>
-      </c>
-      <c r="H40" s="20">
-        <v>0</v>
-      </c>
-      <c r="I40" s="20">
-        <v>0</v>
-      </c>
-      <c r="J40" s="21">
+      <c r="E40" s="6">
+        <v>1.41E-3</v>
+      </c>
+      <c r="F40" s="6">
+        <v>1.41E-3</v>
+      </c>
+      <c r="G40" s="6">
+        <v>1.5499999999999999E-3</v>
+      </c>
+      <c r="H40" s="6">
+        <v>1.4599999999999999E-3</v>
+      </c>
+      <c r="I40" s="6">
+        <v>7.0400000000000003E-3</v>
+      </c>
+      <c r="J40" s="7">
         <f t="shared" ref="J40:J49" si="3">AVERAGE(E40:I40)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="17" t="s">
+        <v>2.5739999999999999E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="5">
         <v>500</v>
       </c>
-      <c r="E41" s="20">
-        <v>0</v>
-      </c>
-      <c r="F41" s="20">
-        <v>0</v>
-      </c>
-      <c r="G41" s="20">
-        <v>0</v>
-      </c>
-      <c r="H41" s="20">
-        <v>0</v>
-      </c>
-      <c r="I41" s="20">
-        <v>0</v>
-      </c>
-      <c r="J41" s="21">
+      <c r="E41" s="6">
+        <v>1.42E-3</v>
+      </c>
+      <c r="F41" s="6">
+        <v>1.42E-3</v>
+      </c>
+      <c r="G41" s="6">
+        <v>1.4E-3</v>
+      </c>
+      <c r="H41" s="6">
+        <v>1.57E-3</v>
+      </c>
+      <c r="I41" s="6">
+        <v>1.9E-3</v>
+      </c>
+      <c r="J41" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="17" t="s">
+        <v>1.542E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="5">
         <v>1000</v>
       </c>
-      <c r="E42" s="20">
-        <v>0</v>
-      </c>
-      <c r="F42" s="20">
-        <v>0</v>
-      </c>
-      <c r="G42" s="20">
-        <v>0</v>
-      </c>
-      <c r="H42" s="20">
-        <v>0</v>
-      </c>
-      <c r="I42" s="20">
-        <v>0</v>
-      </c>
-      <c r="J42" s="21">
+      <c r="E42" s="6">
+        <v>1.5900000000000001E-3</v>
+      </c>
+      <c r="F42" s="6">
+        <v>1.5900000000000001E-3</v>
+      </c>
+      <c r="G42" s="6">
+        <v>1.4400000000000001E-3</v>
+      </c>
+      <c r="H42" s="6">
+        <v>1.4E-3</v>
+      </c>
+      <c r="I42" s="6">
+        <v>1.41E-3</v>
+      </c>
+      <c r="J42" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="17" t="s">
+        <v>1.4859999999999999E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="5">
         <v>5000</v>
       </c>
-      <c r="E43" s="20">
-        <v>0</v>
-      </c>
-      <c r="F43" s="20">
-        <v>0</v>
-      </c>
-      <c r="G43" s="20">
-        <v>0</v>
-      </c>
-      <c r="H43" s="20">
-        <v>0</v>
-      </c>
-      <c r="I43" s="20">
-        <v>0</v>
-      </c>
-      <c r="J43" s="21">
+      <c r="E43" s="6">
+        <v>1.65E-3</v>
+      </c>
+      <c r="F43" s="6">
+        <v>1.65E-3</v>
+      </c>
+      <c r="G43" s="6">
+        <v>1.9300000000000001E-3</v>
+      </c>
+      <c r="H43" s="6">
+        <v>1.73E-3</v>
+      </c>
+      <c r="I43" s="6">
+        <v>1.6100000000000001E-3</v>
+      </c>
+      <c r="J43" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="17" t="s">
+        <v>1.7139999999999998E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="5">
         <v>10000</v>
       </c>
-      <c r="E44" s="20">
-        <v>0</v>
-      </c>
-      <c r="F44" s="20">
-        <v>0</v>
-      </c>
-      <c r="G44" s="20">
-        <v>0</v>
-      </c>
-      <c r="H44" s="20">
-        <v>0</v>
-      </c>
-      <c r="I44" s="20">
-        <v>0</v>
-      </c>
-      <c r="J44" s="21">
+      <c r="E44" s="6">
+        <v>8.8539999999999994E-2</v>
+      </c>
+      <c r="F44" s="6">
+        <v>8.8539999999999994E-2</v>
+      </c>
+      <c r="G44" s="6">
+        <v>0.39482</v>
+      </c>
+      <c r="H44" s="6">
+        <v>7.17E-2</v>
+      </c>
+      <c r="I44" s="6">
+        <v>0.10306999999999999</v>
+      </c>
+      <c r="J44" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="22" t="s">
+        <v>0.14933399999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C45" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D45" s="24">
+      <c r="D45" s="10">
         <v>100</v>
       </c>
-      <c r="E45" s="20">
-        <v>0</v>
-      </c>
-      <c r="F45" s="20">
-        <v>0</v>
-      </c>
-      <c r="G45" s="20">
-        <v>0</v>
-      </c>
-      <c r="H45" s="20">
-        <v>0</v>
-      </c>
-      <c r="I45" s="20">
-        <v>0</v>
-      </c>
-      <c r="J45" s="21">
+      <c r="E45" s="6">
+        <v>1.5399999999999999E-3</v>
+      </c>
+      <c r="F45" s="6">
+        <v>1.5399999999999999E-3</v>
+      </c>
+      <c r="G45" s="6">
+        <v>1.4300000000000001E-3</v>
+      </c>
+      <c r="H45" s="6">
+        <v>1.6199999999999999E-3</v>
+      </c>
+      <c r="I45" s="6">
+        <v>1.3699999999999999E-3</v>
+      </c>
+      <c r="J45" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="22" t="s">
+        <v>1.5E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D46" s="24">
+      <c r="D46" s="10">
         <v>500</v>
       </c>
-      <c r="E46" s="20">
-        <v>0</v>
-      </c>
-      <c r="F46" s="20">
-        <v>0</v>
-      </c>
-      <c r="G46" s="20">
-        <v>0</v>
-      </c>
-      <c r="H46" s="20">
-        <v>0</v>
-      </c>
-      <c r="I46" s="20">
-        <v>0</v>
-      </c>
-      <c r="J46" s="21">
+      <c r="E46" s="6">
+        <v>2.3500000000000001E-3</v>
+      </c>
+      <c r="F46" s="6">
+        <v>2.3500000000000001E-3</v>
+      </c>
+      <c r="G46" s="6">
+        <v>1.9499999999999999E-3</v>
+      </c>
+      <c r="H46" s="6">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="I46" s="6">
+        <v>3.6900000000000001E-3</v>
+      </c>
+      <c r="J46" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="22" t="s">
+        <v>2.408E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C47" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="24">
+      <c r="D47" s="10">
         <v>1000</v>
       </c>
-      <c r="E47" s="20">
-        <v>0</v>
-      </c>
-      <c r="F47" s="20">
-        <v>0</v>
-      </c>
-      <c r="G47" s="20">
-        <v>0</v>
-      </c>
-      <c r="H47" s="20">
-        <v>0</v>
-      </c>
-      <c r="I47" s="20">
-        <v>0</v>
-      </c>
-      <c r="J47" s="21">
+      <c r="E47" s="6">
+        <v>7.8200000000000006E-3</v>
+      </c>
+      <c r="F47" s="6">
+        <v>7.8200000000000006E-3</v>
+      </c>
+      <c r="G47" s="6">
+        <v>2.5200000000000001E-3</v>
+      </c>
+      <c r="H47" s="6">
+        <v>2.5100000000000001E-3</v>
+      </c>
+      <c r="I47" s="6">
+        <v>2.0799999999999998E-3</v>
+      </c>
+      <c r="J47" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="22" t="s">
+        <v>4.5500000000000002E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D48" s="24">
+      <c r="D48" s="10">
         <v>5000</v>
       </c>
-      <c r="E48" s="20">
-        <v>0</v>
-      </c>
-      <c r="F48" s="20">
-        <v>0</v>
-      </c>
-      <c r="G48" s="20">
-        <v>0</v>
-      </c>
-      <c r="H48" s="20">
-        <v>0</v>
-      </c>
-      <c r="I48" s="20">
-        <v>0</v>
-      </c>
-      <c r="J48" s="21">
+      <c r="E48" s="6">
+        <v>2E-3</v>
+      </c>
+      <c r="F48" s="6">
+        <v>2E-3</v>
+      </c>
+      <c r="G48" s="6">
+        <v>2.4099999999999998E-3</v>
+      </c>
+      <c r="H48" s="6">
+        <v>1.9E-3</v>
+      </c>
+      <c r="I48" s="6">
+        <v>2.2399999999999998E-3</v>
+      </c>
+      <c r="J48" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="22" t="s">
+        <v>2.1099999999999999E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C49" s="23" t="s">
+      <c r="C49" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D49" s="24">
+      <c r="D49" s="10">
         <v>10000</v>
       </c>
-      <c r="E49" s="20">
-        <v>0</v>
-      </c>
-      <c r="F49" s="20">
-        <v>0</v>
-      </c>
-      <c r="G49" s="20">
-        <v>0</v>
-      </c>
-      <c r="H49" s="20">
-        <v>0</v>
-      </c>
-      <c r="I49" s="20">
-        <v>0</v>
-      </c>
-      <c r="J49" s="21">
+      <c r="E49" s="6">
+        <v>1.5E-3</v>
+      </c>
+      <c r="F49" s="6">
+        <v>1.5E-3</v>
+      </c>
+      <c r="G49" s="6">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="H49" s="6">
+        <v>1.5900000000000001E-3</v>
+      </c>
+      <c r="I49" s="6">
+        <v>1.4499999999999999E-3</v>
+      </c>
+      <c r="J49" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B52" s="6" t="s">
+        <v>1.6280000000000003E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B52" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="39"/>
+      <c r="I52" s="39"/>
+      <c r="J52" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4864,7 +4864,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -4872,120 +4872,120 @@
     <col min="5" max="13" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="7" t="s">
+    <row r="1" spans="2:4" ht="33.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="17" t="s">
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+    </row>
+    <row r="2" spans="2:4" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="15" t="s">
+    <row r="3" spans="2:4" ht="9.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:4" ht="30.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="26">
+    <row r="5" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="12">
         <v>5</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="13">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A1 - Factorial",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B5)</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="28">
+        <v>2.6200000000000003E-4</v>
+      </c>
+      <c r="D5" s="14">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A1 - Factorial",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="29">
+        <v>2.4399999999999999E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="15">
         <v>10</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="16">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A1 - Factorial",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B6)</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="31">
+        <v>2.1400000000000004E-3</v>
+      </c>
+      <c r="D6" s="17">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A1 - Factorial",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="26">
+        <v>2.6600000000000001E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="12">
         <v>15</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="13">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A1 - Factorial",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B7)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="28">
+        <v>3.6400000000000001E-4</v>
+      </c>
+      <c r="D7" s="14">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A1 - Factorial",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="29">
+        <v>2.9199999999999994E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="15">
         <v>20</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="16">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A1 - Factorial",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B8)</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="31">
+        <v>4.4800000000000005E-4</v>
+      </c>
+      <c r="D8" s="17">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A1 - Factorial",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="26">
+        <v>3.3799999999999998E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="12">
         <v>25</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="13">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A1 - Factorial",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B9)</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="28">
+        <v>5.04E-4</v>
+      </c>
+      <c r="D9" s="14">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A1 - Factorial",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="29">
+        <v>3.4600000000000001E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="15">
         <v>30</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="16">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A1 - Factorial",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B10)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="31">
+        <v>0.19064</v>
+      </c>
+      <c r="D10" s="17">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A1 - Factorial",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="5" t="s">
+        <v>3.1099999999999995E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="39.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5001,7 +5001,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -5009,120 +5009,120 @@
     <col min="5" max="13" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="7" t="s">
+    <row r="1" spans="2:4" ht="33.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="17" t="s">
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+    </row>
+    <row r="2" spans="2:4" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="18" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="15" t="s">
+    <row r="3" spans="2:4" ht="9.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:4" ht="30.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="26">
+    <row r="5" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="12">
         <v>5</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="13">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A2 - Fibonacci",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B5)</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="33">
+        <v>2.8799999999999995E-4</v>
+      </c>
+      <c r="D5" s="19">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A2 - Fibonacci",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="29">
+        <v>2.0800000000000001E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="15">
         <v>10</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="16">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A2 - Fibonacci",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B6)</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="34">
+        <v>5.62E-4</v>
+      </c>
+      <c r="D6" s="20">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A2 - Fibonacci",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="26">
+        <v>5.2599999999999999E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="12">
         <v>15</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="13">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A2 - Fibonacci",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B7)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="33">
+        <v>5.6519999999999999E-3</v>
+      </c>
+      <c r="D7" s="19">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A2 - Fibonacci",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="29">
+        <v>5.7959999999999999E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="15">
         <v>20</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="16">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A2 - Fibonacci",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B8)</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="34">
+        <v>4.7800000000000002E-4</v>
+      </c>
+      <c r="D8" s="20">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A2 - Fibonacci",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="26">
+        <v>5.5909999999999994E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="12">
         <v>25</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="13">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A2 - Fibonacci",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B9)</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="33">
+        <v>1.3100000000000002E-3</v>
+      </c>
+      <c r="D9" s="19">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A2 - Fibonacci",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="29">
+        <v>0.42469999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="15">
         <v>30</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="16">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A2 - Fibonacci",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B10)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="34">
+        <v>1.16E-3</v>
+      </c>
+      <c r="D10" s="20">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A2 - Fibonacci",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="5" t="s">
+        <v>4.9792620000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="39.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5138,7 +5138,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -5146,107 +5146,107 @@
     <col min="5" max="13" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="7" t="s">
+    <row r="1" spans="2:4" ht="33.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="17" t="s">
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+    </row>
+    <row r="2" spans="2:4" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="15" t="s">
+    <row r="3" spans="2:4" ht="9.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:4" ht="30.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="26">
+    <row r="5" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="12">
         <v>100</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="13">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A3 - Busqueda Lineal",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B5)</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="28">
+        <v>2.4200000000000003E-4</v>
+      </c>
+      <c r="D5" s="14">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A3 - Busqueda Lineal",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="29">
+        <v>6.2399999999999988E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="15">
         <v>500</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="16">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A3 - Busqueda Lineal",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B6)</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="31">
+        <v>2.72E-4</v>
+      </c>
+      <c r="D6" s="17">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A3 - Busqueda Lineal",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="26">
+        <v>3.0800000000000001E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="12">
         <v>1000</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="13">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A3 - Busqueda Lineal",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B7)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="28">
+        <v>2.9599999999999993E-4</v>
+      </c>
+      <c r="D7" s="14">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A3 - Busqueda Lineal",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="29">
+        <v>5.0600000000000005E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="15">
         <v>5000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="16">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A3 - Busqueda Lineal",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B8)</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="31">
+        <v>2.8399999999999996E-4</v>
+      </c>
+      <c r="D8" s="17">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A3 - Busqueda Lineal",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="26">
+        <v>3.9199999999999999E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="12">
         <v>10000</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="13">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A3 - Busqueda Lineal",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B9)</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="28">
+        <v>7.2399999999999993E-4</v>
+      </c>
+      <c r="D9" s="14">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A3 - Busqueda Lineal",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="5" t="s">
+        <v>9.1E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="39.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5262,7 +5262,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -5270,107 +5270,107 @@
     <col min="5" max="13" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="7" t="s">
+    <row r="1" spans="2:4" ht="33.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="17" t="s">
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+    </row>
+    <row r="2" spans="2:4" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="15" t="s">
+    <row r="3" spans="2:4" ht="9.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:4" ht="30.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="26">
+    <row r="5" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="12">
         <v>100</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="13">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A4 - Burbuja",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B5)</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="28">
+        <v>2.5739999999999999E-3</v>
+      </c>
+      <c r="D5" s="14">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A4 - Burbuja",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="29">
+        <v>1.5E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="15">
         <v>500</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="16">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A4 - Burbuja",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B6)</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="31">
+        <v>1.542E-3</v>
+      </c>
+      <c r="D6" s="17">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A4 - Burbuja",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="26">
+        <v>2.408E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="12">
         <v>1000</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="13">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A4 - Burbuja",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B7)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="28">
+        <v>1.4859999999999999E-3</v>
+      </c>
+      <c r="D7" s="14">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A4 - Burbuja",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="29">
+        <v>4.5500000000000002E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="15">
         <v>5000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="16">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A4 - Burbuja",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B8)</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="31">
+        <v>1.7139999999999998E-3</v>
+      </c>
+      <c r="D8" s="17">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A4 - Burbuja",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="26">
+        <v>2.1099999999999999E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="12">
         <v>10000</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="13">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A4 - Burbuja",'1. Datos_Crudos'!$C:$C,"Iterativo",'1. Datos_Crudos'!$D:$D,B9)</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="28">
+        <v>0.14933399999999999</v>
+      </c>
+      <c r="D9" s="14">
         <f>AVERAGEIFS('1. Datos_Crudos'!$J:$J,'1. Datos_Crudos'!$B:$B,"A4 - Burbuja",'1. Datos_Crudos'!$C:$C,"Recursivo",'1. Datos_Crudos'!$D:$D,B9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="5" t="s">
+        <v>1.6280000000000003E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="39.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5386,7 +5386,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:G19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -5396,239 +5396,239 @@
     <col min="7" max="7" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="7" t="s">
+    <row r="1" spans="2:7" ht="33.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-    </row>
-    <row r="2" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="35" t="s">
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+    </row>
+    <row r="2" spans="2:7" ht="9.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" ht="30.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="23" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="37" t="s">
+    <row r="4" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="41"/>
-    </row>
-    <row r="5" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="42" t="s">
+      <c r="G4" s="27"/>
+    </row>
+    <row r="5" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="41"/>
-    </row>
-    <row r="6" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="37" t="s">
+      <c r="G5" s="27"/>
+    </row>
+    <row r="6" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="41"/>
-    </row>
-    <row r="7" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="42" t="s">
+      <c r="G6" s="27"/>
+    </row>
+    <row r="7" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="41"/>
-    </row>
-    <row r="8" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="37" t="s">
+      <c r="G7" s="27"/>
+    </row>
+    <row r="8" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="40" t="s">
+      <c r="F8" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="41"/>
-    </row>
-    <row r="9" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="42" t="s">
+      <c r="G8" s="27"/>
+    </row>
+    <row r="9" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="41"/>
-    </row>
-    <row r="10" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="37" t="s">
+      <c r="G9" s="27"/>
+    </row>
+    <row r="10" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="41"/>
-    </row>
-    <row r="11" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="42" t="s">
+      <c r="G10" s="27"/>
+    </row>
+    <row r="11" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="41"/>
-    </row>
-    <row r="14" spans="2:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="4" t="s">
+      <c r="G11" s="27"/>
+    </row>
+    <row r="14" spans="2:7" ht="7.55" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:7" ht="15.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="17" t="s">
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+    </row>
+    <row r="16" spans="2:7" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="22" t="s">
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+    </row>
+    <row r="17" spans="2:7" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="17" t="s">
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+    </row>
+    <row r="18" spans="2:7" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="44" t="s">
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+    </row>
+    <row r="19" spans="2:7" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/Tiempos Rendimiento.xlsx
+++ b/Tiempos Rendimiento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celes\Desktop\IterativoVsRecursivo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A624E3A8-AA17-48F4-8D66-C331DAE2A9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D443BAE2-3161-4C83-AC77-E92C75647106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12509" yWindow="75" windowWidth="11533" windowHeight="12722" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guia de Uso" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="74">
   <si>
     <t>GUIA DE USO — Ejemplo de Registro de Tiempos de Ejecucion</t>
   </si>
@@ -234,12 +234,6 @@
     <t>Justificacion breve</t>
   </si>
   <si>
-    <t>(escribe aqui)</t>
-  </si>
-  <si>
-    <t>Si / No</t>
-  </si>
-  <si>
     <t>O(2^n)</t>
   </si>
   <si>
@@ -268,6 +262,33 @@
   </si>
   <si>
     <t>→  Big-O es probablemente O(2^n)</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>Es lineal, con menor pila</t>
+  </si>
+  <si>
+    <t>Lineal con riesgo de overflow</t>
+  </si>
+  <si>
+    <t>Eficiente en memoria y tiempo</t>
+  </si>
+  <si>
+    <t>Crecimiento exponencial por llamadas duplicadas</t>
+  </si>
+  <si>
+    <t>Mayor uso de pila, no aporta ventaja</t>
+  </si>
+  <si>
+    <t>Eficiente en memoria</t>
+  </si>
+  <si>
+    <t>Al multiplicar n*10 el tiempo aumenta</t>
+  </si>
+  <si>
+    <t>Con overhead</t>
   </si>
 </sst>
 </file>
@@ -3031,8 +3052,8 @@
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>555120</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>24120</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>111584</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5016,7 +5037,7 @@
       <c r="C1" s="38"/>
       <c r="D1" s="38"/>
     </row>
-    <row r="2" spans="2:4" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4" ht="44.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>32</v>
       </c>
@@ -5435,15 +5456,17 @@
         <v>25</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="27"/>
+        <v>65</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="5" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="28" t="s">
@@ -5453,15 +5476,17 @@
         <v>26</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E5" s="28" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" s="27"/>
+        <v>65</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="6" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="23" t="s">
@@ -5471,15 +5496,17 @@
         <v>25</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E6" s="23" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="27"/>
+        <v>65</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="7" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="28" t="s">
@@ -5492,12 +5519,14 @@
         <v>55</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="27"/>
+        <v>65</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="8" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="23" t="s">
@@ -5507,15 +5536,17 @@
         <v>25</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="27"/>
+        <v>65</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="9" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="28" t="s">
@@ -5525,15 +5556,17 @@
         <v>26</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E9" s="28" t="s">
         <v>33</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="27"/>
+        <v>65</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="10" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="23" t="s">
@@ -5543,15 +5576,17 @@
         <v>25</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E10" s="23" t="s">
         <v>45</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="27"/>
+        <v>65</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="11" spans="2:7" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
@@ -5561,20 +5596,22 @@
         <v>26</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E11" s="28" t="s">
         <v>45</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="27"/>
+        <v>65</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="14" spans="2:7" ht="7.55" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="2:7" ht="15.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="42" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C15" s="42"/>
       <c r="D15" s="42"/>
@@ -5584,10 +5621,10 @@
     </row>
     <row r="16" spans="2:7" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D16" s="43"/>
       <c r="E16" s="43"/>
@@ -5596,10 +5633,10 @@
     </row>
     <row r="17" spans="2:7" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D17" s="44"/>
       <c r="E17" s="44"/>
@@ -5608,10 +5645,10 @@
     </row>
     <row r="18" spans="2:7" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D18" s="43"/>
       <c r="E18" s="43"/>
@@ -5620,10 +5657,10 @@
     </row>
     <row r="19" spans="2:7" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D19" s="41"/>
       <c r="E19" s="41"/>
